--- a/AAII_Financials/Quarterly/CBDS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBDS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
   <si>
     <t>CBDS</t>
   </si>
@@ -656,136 +656,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -799,37 +803,37 @@
         <v>300</v>
       </c>
       <c r="G8" s="3">
+        <v>300</v>
+      </c>
+      <c r="H8" s="3">
         <v>400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>500</v>
-      </c>
-      <c r="I8" s="3">
-        <v>400</v>
       </c>
       <c r="J8" s="3">
         <v>400</v>
       </c>
       <c r="K8" s="3">
+        <v>400</v>
+      </c>
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>500</v>
       </c>
       <c r="R8" s="3">
         <v>500</v>
@@ -838,11 +842,11 @@
         <v>500</v>
       </c>
       <c r="T8" s="3">
+        <v>500</v>
+      </c>
+      <c r="U8" s="3">
         <v>200</v>
       </c>
-      <c r="U8" s="3">
-        <v>100</v>
-      </c>
       <c r="V8" s="3">
         <v>100</v>
       </c>
@@ -850,19 +854,19 @@
         <v>100</v>
       </c>
       <c r="X8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y8" s="3">
         <v>300</v>
       </c>
-      <c r="Y8" s="3">
-        <v>100</v>
-      </c>
       <c r="Z8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA8" s="3">
         <v>200</v>
       </c>
-      <c r="AA8" s="3">
-        <v>100</v>
-      </c>
       <c r="AB8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC8" s="3">
         <v>0</v>
@@ -873,8 +877,11 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -891,34 +898,34 @@
         <v>100</v>
       </c>
       <c r="H9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I9" s="3">
         <v>200</v>
       </c>
       <c r="J9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K9" s="3">
+        <v>100</v>
+      </c>
+      <c r="L9" s="3">
         <v>200</v>
-      </c>
-      <c r="L9" s="3">
-        <v>400</v>
       </c>
       <c r="M9" s="3">
         <v>400</v>
       </c>
       <c r="N9" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="O9" s="3">
+        <v>100</v>
+      </c>
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>400</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>200</v>
       </c>
       <c r="R9" s="3">
         <v>200</v>
@@ -927,31 +934,31 @@
         <v>200</v>
       </c>
       <c r="T9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9" s="3">
         <v>0</v>
       </c>
       <c r="W9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X9" s="3">
         <v>100</v>
       </c>
       <c r="Y9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="3">
         <v>100</v>
       </c>
       <c r="AB9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC9" s="3">
         <v>0</v>
@@ -962,8 +969,11 @@
       <c r="AE9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -977,37 +987,37 @@
         <v>200</v>
       </c>
       <c r="G10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H10" s="3">
         <v>300</v>
       </c>
       <c r="I10" s="3">
+        <v>300</v>
+      </c>
+      <c r="J10" s="3">
         <v>200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>300</v>
       </c>
       <c r="K10" s="3">
         <v>300</v>
       </c>
       <c r="L10" s="3">
+        <v>300</v>
+      </c>
+      <c r="M10" s="3">
         <v>600</v>
       </c>
-      <c r="M10" s="3">
-        <v>100</v>
-      </c>
       <c r="N10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O10" s="3">
         <v>200</v>
       </c>
       <c r="P10" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q10" s="3">
         <v>800</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>300</v>
       </c>
       <c r="R10" s="3">
         <v>300</v>
@@ -1016,7 +1026,7 @@
         <v>300</v>
       </c>
       <c r="T10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U10" s="3">
         <v>100</v>
@@ -1025,19 +1035,19 @@
         <v>100</v>
       </c>
       <c r="W10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
         <v>200</v>
       </c>
-      <c r="Y10" s="3">
-        <v>100</v>
-      </c>
       <c r="Z10" s="3">
         <v>100</v>
       </c>
       <c r="AA10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB10" s="3">
         <v>0</v>
@@ -1051,8 +1061,11 @@
       <c r="AE10" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,19 +1279,22 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1285,11 +1305,11 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1297,11 +1317,11 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1309,50 +1329,53 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>1400</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>1200</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>900</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1381,13 +1404,13 @@
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3">
         <v>100</v>
@@ -1398,8 +1421,8 @@
       <c r="Q15" s="3">
         <v>100</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>8</v>
+      <c r="R15" s="3">
+        <v>100</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>8</v>
@@ -1413,8 +1436,8 @@
       <c r="V15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,8 +1496,9 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1479,19 +1506,19 @@
         <v>600</v>
       </c>
       <c r="E17" s="3">
+        <v>600</v>
+      </c>
+      <c r="F17" s="3">
         <v>500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>600</v>
-      </c>
-      <c r="I17" s="3">
-        <v>800</v>
       </c>
       <c r="J17" s="3">
         <v>800</v>
@@ -1500,67 +1527,70 @@
         <v>800</v>
       </c>
       <c r="L17" s="3">
+        <v>800</v>
+      </c>
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1900</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>2000</v>
       </c>
       <c r="AD17" s="3">
         <v>2000</v>
       </c>
       <c r="AE17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AF17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1568,88 +1598,91 @@
         <v>-300</v>
       </c>
       <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-200</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-400</v>
       </c>
       <c r="G18" s="3">
         <v>-400</v>
       </c>
       <c r="H18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-400</v>
       </c>
       <c r="J18" s="3">
         <v>-400</v>
       </c>
       <c r="K18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1900</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-2000</v>
       </c>
       <c r="AD18" s="3">
         <v>-2000</v>
       </c>
       <c r="AE18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,47 +1714,48 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>100</v>
-      </c>
       <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1729,13 +1763,13 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>-100</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -1747,13 +1781,13 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3">
         <v>200</v>
       </c>
       <c r="Z20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
@@ -1770,40 +1804,43 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-600</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-300</v>
       </c>
       <c r="N21" s="3">
         <v>-300</v>
@@ -1812,55 +1849,58 @@
         <v>-300</v>
       </c>
       <c r="P21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2000</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-400</v>
       </c>
       <c r="T21" s="3">
         <v>-400</v>
       </c>
       <c r="U21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V21" s="3">
         <v>-600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1927,11 +1967,11 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -1943,102 +1983,108 @@
         <v>0</v>
       </c>
       <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
         <v>300</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-300</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-400</v>
       </c>
       <c r="O23" s="3">
         <v>-400</v>
       </c>
       <c r="P23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,129 +2264,135 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-300</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-400</v>
       </c>
       <c r="O26" s="3">
         <v>-400</v>
       </c>
       <c r="P26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-800</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-300</v>
       </c>
       <c r="N27" s="3">
         <v>-300</v>
@@ -2346,55 +2401,58 @@
         <v>-300</v>
       </c>
       <c r="P27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2493,8 +2554,8 @@
       <c r="E29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -2512,26 +2573,26 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-100</v>
-      </c>
-      <c r="M29" s="3">
-        <v>-200</v>
       </c>
       <c r="N29" s="3">
         <v>-200</v>
       </c>
       <c r="O29" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="P29" s="3">
         <v>-300</v>
       </c>
       <c r="Q29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R29" s="3">
         <v>-100</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
@@ -2553,8 +2614,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2565,14 +2626,17 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,47 +2816,50 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2797,13 +2867,13 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>100</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U32" s="3">
         <v>0</v>
@@ -2815,13 +2885,13 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="3">
         <v>-200</v>
       </c>
       <c r="Z32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
@@ -2838,97 +2908,103 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,8 +3351,9 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3280,7 +3367,7 @@
         <v>100</v>
       </c>
       <c r="G41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H41" s="3">
         <v>200</v>
@@ -3292,7 +3379,7 @@
         <v>200</v>
       </c>
       <c r="K41" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L41" s="3">
         <v>300</v>
@@ -3304,58 +3391,61 @@
         <v>300</v>
       </c>
       <c r="O41" s="3">
+        <v>300</v>
+      </c>
+      <c r="P41" s="3">
         <v>400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>500</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>300</v>
       </c>
       <c r="R41" s="3">
         <v>300</v>
       </c>
       <c r="S41" s="3">
+        <v>300</v>
+      </c>
+      <c r="T41" s="3">
         <v>200</v>
       </c>
-      <c r="T41" s="3">
-        <v>100</v>
-      </c>
       <c r="U41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V41" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W41" s="3">
         <v>200</v>
       </c>
       <c r="X41" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y41" s="3">
         <v>100</v>
       </c>
       <c r="Z41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA41" s="3">
         <v>200</v>
       </c>
       <c r="AB41" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC41" s="3">
         <v>400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>300</v>
       </c>
-      <c r="AE41" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3366,19 +3456,19 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>500</v>
-      </c>
-      <c r="J42" s="3">
-        <v>200</v>
       </c>
       <c r="K42" s="3">
         <v>200</v>
@@ -3387,13 +3477,13 @@
         <v>200</v>
       </c>
       <c r="M42" s="3">
+        <v>200</v>
+      </c>
+      <c r="N42" s="3">
         <v>300</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>8</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>8</v>
@@ -3404,11 +3494,11 @@
       <c r="R42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S42" s="3">
-        <v>100</v>
+      <c r="S42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T42" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U42" s="3">
         <v>200</v>
@@ -3416,8 +3506,8 @@
       <c r="V42" s="3">
         <v>200</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>8</v>
+      <c r="W42" s="3">
+        <v>200</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>8</v>
@@ -3425,8 +3515,8 @@
       <c r="Y42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -3443,8 +3533,11 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3532,8 +3625,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3568,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O44" s="3">
         <v>100</v>
@@ -3580,7 +3676,7 @@
         <v>100</v>
       </c>
       <c r="R44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -3621,16 +3717,19 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
         <v>0</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
+      <c r="E45" s="3">
+        <v>0</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
@@ -3644,20 +3743,20 @@
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3">
-        <v>100</v>
+      <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O45" s="3">
         <v>0</v>
@@ -3669,10 +3768,10 @@
         <v>0</v>
       </c>
       <c r="R45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
@@ -3684,78 +3783,81 @@
         <v>0</v>
       </c>
       <c r="W45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X45" s="3">
         <v>100</v>
       </c>
       <c r="Y45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z45" s="3">
         <v>900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1200</v>
       </c>
-      <c r="AB45" s="3">
-        <v>100</v>
-      </c>
       <c r="AC45" s="3">
         <v>100</v>
       </c>
       <c r="AD45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE45" s="3">
         <v>200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E46" s="3">
         <v>100</v>
       </c>
       <c r="F46" s="3">
+        <v>100</v>
+      </c>
+      <c r="G46" s="3">
         <v>500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>400</v>
-      </c>
-      <c r="K46" s="3">
-        <v>500</v>
       </c>
       <c r="L46" s="3">
         <v>500</v>
       </c>
       <c r="M46" s="3">
+        <v>500</v>
+      </c>
+      <c r="N46" s="3">
         <v>700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>400</v>
-      </c>
-      <c r="O46" s="3">
-        <v>500</v>
       </c>
       <c r="P46" s="3">
         <v>500</v>
       </c>
       <c r="Q46" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="R46" s="3">
         <v>400</v>
@@ -3764,43 +3866,46 @@
         <v>400</v>
       </c>
       <c r="T46" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="U46" s="3">
         <v>300</v>
       </c>
       <c r="V46" s="3">
+        <v>300</v>
+      </c>
+      <c r="W46" s="3">
         <v>400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3825,21 +3930,21 @@
       <c r="J47" s="3">
         <v>0</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>800</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3">
         <v>200</v>
       </c>
-      <c r="O47" s="3">
-        <v>100</v>
-      </c>
       <c r="P47" s="3">
         <v>100</v>
       </c>
@@ -3847,10 +3952,10 @@
         <v>100</v>
       </c>
       <c r="R47" s="3">
-        <v>0</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>8</v>
@@ -3861,8 +3966,8 @@
       <c r="V47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W47" s="3">
-        <v>200</v>
+      <c r="W47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X47" s="3">
         <v>200</v>
@@ -3871,7 +3976,7 @@
         <v>200</v>
       </c>
       <c r="Z47" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -3888,8 +3993,11 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3906,10 +4014,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>0</v>
@@ -3921,23 +4029,23 @@
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3">
         <v>200</v>
       </c>
       <c r="O48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>300</v>
       </c>
       <c r="Q48" s="3">
+        <v>300</v>
+      </c>
+      <c r="R48" s="3">
         <v>200</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
       <c r="S48" s="3">
         <v>0</v>
       </c>
@@ -3977,8 +4085,11 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3986,7 +4097,7 @@
         <v>1900</v>
       </c>
       <c r="E49" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="F49" s="3">
         <v>2000</v>
@@ -3995,13 +4106,13 @@
         <v>2000</v>
       </c>
       <c r="H49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="I49" s="3">
         <v>2100</v>
       </c>
       <c r="J49" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="K49" s="3">
         <v>2200</v>
@@ -4010,64 +4121,67 @@
         <v>2200</v>
       </c>
       <c r="M49" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="N49" s="3">
         <v>2300</v>
       </c>
       <c r="O49" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="P49" s="3">
         <v>2400</v>
       </c>
       <c r="Q49" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="R49" s="3">
         <v>2500</v>
       </c>
       <c r="S49" s="3">
+        <v>2500</v>
+      </c>
+      <c r="T49" s="3">
         <v>4000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4258,8 +4378,8 @@
       <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
+      <c r="G52" s="3">
+        <v>100</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>8</v>
@@ -4267,8 +4387,8 @@
       <c r="I52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4280,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
@@ -4291,8 +4411,8 @@
       <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
+      <c r="R52" s="3">
+        <v>100</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>8</v>
@@ -4306,8 +4426,8 @@
       <c r="V52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,8 +4545,11 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4431,88 +4557,91 @@
         <v>2100</v>
       </c>
       <c r="E54" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F54" s="3">
         <v>2200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,8 +4707,9 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4589,11 +4720,11 @@
         <v>100</v>
       </c>
       <c r="F57" s="3">
+        <v>100</v>
+      </c>
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
-        <v>100</v>
-      </c>
       <c r="H57" s="3">
         <v>100</v>
       </c>
@@ -4607,7 +4738,7 @@
         <v>100</v>
       </c>
       <c r="L57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
@@ -4619,19 +4750,19 @@
         <v>200</v>
       </c>
       <c r="P57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
       </c>
       <c r="R57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>200</v>
       </c>
       <c r="T57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U57" s="3">
         <v>100</v>
@@ -4643,19 +4774,19 @@
         <v>100</v>
       </c>
       <c r="X57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y57" s="3">
         <v>200</v>
       </c>
-      <c r="Y57" s="3">
-        <v>100</v>
-      </c>
       <c r="Z57" s="3">
         <v>100</v>
       </c>
       <c r="AA57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB57" s="3">
         <v>300</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>200</v>
       </c>
       <c r="AC57" s="3">
         <v>200</v>
@@ -4664,30 +4795,33 @@
         <v>200</v>
       </c>
       <c r="AE57" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AF57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
         <v>400</v>
       </c>
       <c r="F58" s="3">
+        <v>400</v>
+      </c>
+      <c r="G58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
-        <v>100</v>
-      </c>
       <c r="I58" s="3">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>1200</v>
@@ -4708,13 +4842,13 @@
         <v>1200</v>
       </c>
       <c r="P58" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="Q58" s="3">
         <v>1100</v>
       </c>
       <c r="R58" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="S58" s="3">
         <v>1000</v>
@@ -4723,7 +4857,7 @@
         <v>1000</v>
       </c>
       <c r="U58" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="V58" s="3">
         <v>900</v>
@@ -4732,31 +4866,34 @@
         <v>900</v>
       </c>
       <c r="X58" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="Y58" s="3">
         <v>800</v>
       </c>
       <c r="Z58" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA58" s="3">
         <v>600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>300</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>500</v>
       </c>
       <c r="AD58" s="3">
         <v>500</v>
       </c>
       <c r="AE58" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF58" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4776,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3">
         <v>200</v>
@@ -4788,69 +4925,72 @@
         <v>200</v>
       </c>
       <c r="M59" s="3">
+        <v>200</v>
+      </c>
+      <c r="N59" s="3">
         <v>300</v>
-      </c>
-      <c r="N59" s="3">
-        <v>200</v>
       </c>
       <c r="O59" s="3">
         <v>200</v>
       </c>
       <c r="P59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q59" s="3">
         <v>100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="R59" s="3">
+        <v>100</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T59" s="3">
         <v>500</v>
-      </c>
-      <c r="T59" s="3">
-        <v>400</v>
       </c>
       <c r="U59" s="3">
         <v>400</v>
       </c>
       <c r="V59" s="3">
+        <v>400</v>
+      </c>
+      <c r="W59" s="3">
         <v>500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1000</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>800</v>
       </c>
       <c r="Z59" s="3">
         <v>800</v>
       </c>
       <c r="AA59" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB59" s="3">
         <v>1000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>500</v>
       </c>
-      <c r="AC59" s="3">
-        <v>100</v>
-      </c>
       <c r="AD59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE59" s="3">
         <v>200</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E60" s="3">
         <v>500</v>
@@ -4859,16 +4999,16 @@
         <v>500</v>
       </c>
       <c r="G60" s="3">
+        <v>500</v>
+      </c>
+      <c r="H60" s="3">
         <v>400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1600</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1500</v>
       </c>
       <c r="K60" s="3">
         <v>1500</v>
@@ -4877,64 +5017,67 @@
         <v>1500</v>
       </c>
       <c r="M60" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="N60" s="3">
         <v>1600</v>
       </c>
       <c r="O60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P60" s="3">
         <v>1500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1600</v>
-      </c>
-      <c r="T60" s="3">
-        <v>1500</v>
       </c>
       <c r="U60" s="3">
         <v>1500</v>
       </c>
       <c r="V60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W60" s="3">
         <v>1600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5022,32 +5165,35 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>700</v>
+      </c>
+      <c r="E62" s="3">
         <v>500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>400</v>
       </c>
       <c r="F62" s="3">
         <v>400</v>
       </c>
       <c r="G62" s="3">
+        <v>400</v>
+      </c>
+      <c r="H62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>200</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
       <c r="K62" s="3">
         <v>0</v>
       </c>
@@ -5070,11 +5216,11 @@
         <v>0</v>
       </c>
       <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>600</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5090,8 +5236,8 @@
       <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,31 +5533,34 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3100</v>
-      </c>
-      <c r="J66" s="3">
-        <v>2900</v>
       </c>
       <c r="K66" s="3">
         <v>2900</v>
@@ -5411,7 +5569,7 @@
         <v>2900</v>
       </c>
       <c r="M66" s="3">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="N66" s="3">
         <v>2600</v>
@@ -5420,55 +5578,58 @@
         <v>2600</v>
       </c>
       <c r="P66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Q66" s="3">
         <v>2700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2800</v>
-      </c>
-      <c r="T66" s="3">
-        <v>2700</v>
       </c>
       <c r="U66" s="3">
         <v>2700</v>
       </c>
       <c r="V66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="W66" s="3">
         <v>2800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-81700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-81500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-81100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-80600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-80000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-79900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-79600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-79500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-79100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-77900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-77400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-77000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-76500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-76000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-75500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-74900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-72700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-72200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-71600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-70900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-69600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-68800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-67800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-66800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-64200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-63200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-61200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-59200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-54900</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,37 +6395,40 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E76" s="3">
         <v>-300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>400</v>
-      </c>
-      <c r="G76" s="3">
-        <v>1000</v>
       </c>
       <c r="H76" s="3">
         <v>1000</v>
       </c>
       <c r="I76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J76" s="3">
         <v>-400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-200</v>
-      </c>
-      <c r="L76" s="3">
-        <v>700</v>
       </c>
       <c r="M76" s="3">
         <v>700</v>
@@ -6260,49 +6446,52 @@
         <v>700</v>
       </c>
       <c r="R76" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="S76" s="3">
+        <v>0</v>
+      </c>
+      <c r="T76" s="3">
         <v>1600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6636,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
@@ -6672,17 +6871,17 @@
         <v>100</v>
       </c>
       <c r="X83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y83" s="3">
         <v>300</v>
       </c>
-      <c r="Y83" s="3">
-        <v>100</v>
-      </c>
       <c r="Z83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA83" s="3">
         <v>200</v>
       </c>
-      <c r="AA83" s="3">
-        <v>100</v>
-      </c>
       <c r="AB83" s="3">
         <v>100</v>
       </c>
@@ -6690,13 +6889,16 @@
         <v>100</v>
       </c>
       <c r="AD83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE83" s="3">
         <v>300</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,31 +7354,34 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G89" s="3">
         <v>-100</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I89" s="3">
         <v>0</v>
       </c>
       <c r="J89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K89" s="3">
         <v>-100</v>
@@ -7176,28 +7393,28 @@
         <v>-100</v>
       </c>
       <c r="N89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3">
-        <v>100</v>
-      </c>
       <c r="S89" s="3">
         <v>100</v>
       </c>
       <c r="T89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V89" s="3">
         <v>-100</v>
@@ -7206,22 +7423,22 @@
         <v>-100</v>
       </c>
       <c r="X89" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="Y89" s="3">
         <v>-400</v>
       </c>
       <c r="Z89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-100</v>
       </c>
       <c r="AD89" s="3">
         <v>-100</v>
@@ -7229,8 +7446,11 @@
       <c r="AE89" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7294,32 +7515,32 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>8</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -7336,8 +7557,8 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>8</v>
+      <c r="AA91" s="3">
+        <v>0</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>8</v>
@@ -7345,14 +7566,17 @@
       <c r="AC91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7756,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7541,11 +7771,11 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -7577,11 +7807,11 @@
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -7607,19 +7837,22 @@
         <v>0</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-200</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8019,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
         <v>100</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
@@ -8037,16 +8283,16 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M100" s="3">
         <v>100</v>
       </c>
       <c r="N100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P100" s="3">
         <v>100</v>
@@ -8058,7 +8304,7 @@
         <v>100</v>
       </c>
       <c r="S100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -8067,37 +8313,40 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>100</v>
+      </c>
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>400</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>300</v>
       </c>
       <c r="Z100" s="3">
         <v>300</v>
       </c>
       <c r="AA100" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AB100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>300</v>
       </c>
-      <c r="AE100" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,23 +8434,26 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
@@ -8209,11 +8461,11 @@
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
@@ -8221,57 +8473,60 @@
         <v>0</v>
       </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>400</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S102" s="3">
+        <v>100</v>
+      </c>
+      <c r="T102" s="3">
         <v>200</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V102" s="3">
         <v>-100</v>
       </c>
       <c r="W102" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="X102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Y102" s="3">
         <v>-100</v>
       </c>
       <c r="Z102" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="AA102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CBDS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBDS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>CBDS</t>
   </si>
@@ -656,145 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E8" s="3">
         <v>300</v>
@@ -806,37 +809,37 @@
         <v>300</v>
       </c>
       <c r="H8" s="3">
+        <v>300</v>
+      </c>
+      <c r="I8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>500</v>
-      </c>
-      <c r="J8" s="3">
-        <v>400</v>
       </c>
       <c r="K8" s="3">
         <v>400</v>
       </c>
       <c r="L8" s="3">
+        <v>400</v>
+      </c>
+      <c r="M8" s="3">
         <v>500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1200</v>
-      </c>
-      <c r="R8" s="3">
-        <v>500</v>
       </c>
       <c r="S8" s="3">
         <v>500</v>
@@ -845,11 +848,11 @@
         <v>500</v>
       </c>
       <c r="U8" s="3">
+        <v>500</v>
+      </c>
+      <c r="V8" s="3">
         <v>200</v>
       </c>
-      <c r="V8" s="3">
-        <v>100</v>
-      </c>
       <c r="W8" s="3">
         <v>100</v>
       </c>
@@ -857,19 +860,19 @@
         <v>100</v>
       </c>
       <c r="Y8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z8" s="3">
         <v>300</v>
       </c>
-      <c r="Z8" s="3">
-        <v>100</v>
-      </c>
       <c r="AA8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB8" s="3">
         <v>200</v>
       </c>
-      <c r="AB8" s="3">
-        <v>100</v>
-      </c>
       <c r="AC8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
@@ -880,8 +883,11 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -901,34 +907,34 @@
         <v>100</v>
       </c>
       <c r="I9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3">
         <v>200</v>
       </c>
       <c r="K9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L9" s="3">
+        <v>100</v>
+      </c>
+      <c r="M9" s="3">
         <v>200</v>
-      </c>
-      <c r="M9" s="3">
-        <v>400</v>
       </c>
       <c r="N9" s="3">
         <v>400</v>
       </c>
       <c r="O9" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="P9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="3">
         <v>200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>400</v>
-      </c>
-      <c r="R9" s="3">
-        <v>200</v>
       </c>
       <c r="S9" s="3">
         <v>200</v>
@@ -937,31 +943,31 @@
         <v>200</v>
       </c>
       <c r="U9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W9" s="3">
         <v>0</v>
       </c>
       <c r="X9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3">
         <v>100</v>
       </c>
       <c r="Z9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="3">
         <v>100</v>
       </c>
       <c r="AC9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD9" s="3">
         <v>0</v>
@@ -972,13 +978,16 @@
       <c r="AF9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3">
         <v>200</v>
@@ -990,37 +999,37 @@
         <v>200</v>
       </c>
       <c r="H10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I10" s="3">
         <v>300</v>
       </c>
       <c r="J10" s="3">
+        <v>300</v>
+      </c>
+      <c r="K10" s="3">
         <v>200</v>
-      </c>
-      <c r="K10" s="3">
-        <v>300</v>
       </c>
       <c r="L10" s="3">
         <v>300</v>
       </c>
       <c r="M10" s="3">
+        <v>300</v>
+      </c>
+      <c r="N10" s="3">
         <v>600</v>
       </c>
-      <c r="N10" s="3">
-        <v>100</v>
-      </c>
       <c r="O10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P10" s="3">
         <v>200</v>
       </c>
       <c r="Q10" s="3">
+        <v>200</v>
+      </c>
+      <c r="R10" s="3">
         <v>800</v>
-      </c>
-      <c r="R10" s="3">
-        <v>300</v>
       </c>
       <c r="S10" s="3">
         <v>300</v>
@@ -1029,7 +1038,7 @@
         <v>300</v>
       </c>
       <c r="U10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="V10" s="3">
         <v>100</v>
@@ -1038,19 +1047,19 @@
         <v>100</v>
       </c>
       <c r="X10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="3">
         <v>200</v>
       </c>
-      <c r="Z10" s="3">
-        <v>100</v>
-      </c>
       <c r="AA10" s="3">
         <v>100</v>
       </c>
       <c r="AB10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC10" s="3">
         <v>0</v>
@@ -1064,8 +1073,11 @@
       <c r="AF10" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1291,16 +1310,16 @@
         <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1308,11 +1327,11 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1320,11 +1339,11 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1332,50 +1351,53 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>1400</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>1200</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>900</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1407,13 +1429,13 @@
         <v>0</v>
       </c>
       <c r="M15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3">
         <v>100</v>
@@ -1424,8 +1446,8 @@
       <c r="R15" s="3">
         <v>100</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>8</v>
+      <c r="S15" s="3">
+        <v>100</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>8</v>
@@ -1439,8 +1461,8 @@
       <c r="W15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,8 +1522,9 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1509,19 +1535,19 @@
         <v>600</v>
       </c>
       <c r="F17" s="3">
+        <v>600</v>
+      </c>
+      <c r="G17" s="3">
         <v>500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>700</v>
       </c>
       <c r="H17" s="3">
         <v>800</v>
       </c>
       <c r="I17" s="3">
+        <v>800</v>
+      </c>
+      <c r="J17" s="3">
         <v>600</v>
-      </c>
-      <c r="J17" s="3">
-        <v>800</v>
       </c>
       <c r="K17" s="3">
         <v>800</v>
@@ -1530,159 +1556,165 @@
         <v>800</v>
       </c>
       <c r="M17" s="3">
+        <v>800</v>
+      </c>
+      <c r="N17" s="3">
         <v>2000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1900</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>2000</v>
       </c>
       <c r="AE17" s="3">
         <v>2000</v>
       </c>
       <c r="AF17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E18" s="3">
         <v>-300</v>
       </c>
       <c r="F18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-400</v>
       </c>
       <c r="K18" s="3">
         <v>-400</v>
       </c>
       <c r="L18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M18" s="3">
         <v>-300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1900</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-2000</v>
       </c>
       <c r="AE18" s="3">
         <v>-2000</v>
       </c>
       <c r="AF18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1747,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1724,41 +1757,41 @@
         <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
-        <v>100</v>
-      </c>
       <c r="O20" s="3">
+        <v>100</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1766,13 +1799,13 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
         <v>-100</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
@@ -1784,13 +1817,13 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3">
         <v>200</v>
       </c>
       <c r="AA20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB20" s="3">
         <v>0</v>
@@ -1807,43 +1840,46 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="N21" s="3">
         <v>-600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-300</v>
       </c>
       <c r="O21" s="3">
         <v>-300</v>
@@ -1852,60 +1888,63 @@
         <v>-300</v>
       </c>
       <c r="Q21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R21" s="3">
         <v>-700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2000</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-400</v>
       </c>
       <c r="U21" s="3">
         <v>-400</v>
       </c>
       <c r="V21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W21" s="3">
         <v>-600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1970,11 +2009,11 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1986,105 +2025,111 @@
         <v>0</v>
       </c>
       <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
         <v>300</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-500</v>
       </c>
-      <c r="G23" s="3">
-        <v>-700</v>
-      </c>
       <c r="H23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-300</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-400</v>
       </c>
       <c r="P23" s="3">
         <v>-400</v>
       </c>
       <c r="Q23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R23" s="3">
         <v>-900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2220,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,135 +2315,141 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-500</v>
       </c>
-      <c r="G26" s="3">
-        <v>-700</v>
-      </c>
       <c r="H26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-300</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-400</v>
       </c>
       <c r="P26" s="3">
         <v>-400</v>
       </c>
       <c r="Q26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R26" s="3">
         <v>-900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-500</v>
       </c>
-      <c r="G27" s="3">
-        <v>-600</v>
-      </c>
       <c r="H27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-800</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-300</v>
       </c>
       <c r="O27" s="3">
         <v>-300</v>
@@ -2404,55 +2458,58 @@
         <v>-300</v>
       </c>
       <c r="Q27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2557,8 +2617,8 @@
       <c r="F29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -2576,26 +2636,26 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-100</v>
-      </c>
-      <c r="N29" s="3">
-        <v>-200</v>
       </c>
       <c r="O29" s="3">
         <v>-200</v>
       </c>
       <c r="P29" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="Q29" s="3">
         <v>-300</v>
       </c>
       <c r="R29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S29" s="3">
         <v>-100</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
         <v>0</v>
       </c>
@@ -2617,8 +2677,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2629,14 +2689,17 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2885,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2828,41 +2897,41 @@
         <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2870,13 +2939,13 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
         <v>100</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
@@ -2888,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3">
         <v>-200</v>
       </c>
       <c r="AA32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AB32" s="3">
         <v>0</v>
@@ -2911,100 +2980,106 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-600</v>
       </c>
-      <c r="H33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="R33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="S33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="U33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="X33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-400</v>
       </c>
-      <c r="J33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-400</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="Z33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AE33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-500</v>
       </c>
-      <c r="P33" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-600</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-500</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-700</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-600</v>
       </c>
-      <c r="H35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="R35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="S35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="U35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="X35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-400</v>
       </c>
-      <c r="J35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-400</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="Z35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AE35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-500</v>
       </c>
-      <c r="P35" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-600</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-500</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-700</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,8 +3437,9 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3370,7 +3456,7 @@
         <v>100</v>
       </c>
       <c r="H41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I41" s="3">
         <v>200</v>
@@ -3382,7 +3468,7 @@
         <v>200</v>
       </c>
       <c r="L41" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M41" s="3">
         <v>300</v>
@@ -3394,63 +3480,66 @@
         <v>300</v>
       </c>
       <c r="P41" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q41" s="3">
         <v>400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>500</v>
-      </c>
-      <c r="R41" s="3">
-        <v>300</v>
       </c>
       <c r="S41" s="3">
         <v>300</v>
       </c>
       <c r="T41" s="3">
+        <v>300</v>
+      </c>
+      <c r="U41" s="3">
         <v>200</v>
       </c>
-      <c r="U41" s="3">
-        <v>100</v>
-      </c>
       <c r="V41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W41" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="X41" s="3">
         <v>200</v>
       </c>
       <c r="Y41" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z41" s="3">
         <v>100</v>
       </c>
       <c r="AA41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB41" s="3">
         <v>200</v>
       </c>
       <c r="AC41" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD41" s="3">
         <v>400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>300</v>
       </c>
-      <c r="AF41" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -3459,19 +3548,19 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>500</v>
-      </c>
-      <c r="K42" s="3">
-        <v>200</v>
       </c>
       <c r="L42" s="3">
         <v>200</v>
@@ -3480,13 +3569,13 @@
         <v>200</v>
       </c>
       <c r="N42" s="3">
+        <v>200</v>
+      </c>
+      <c r="O42" s="3">
         <v>300</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>8</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>8</v>
@@ -3497,11 +3586,11 @@
       <c r="S42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T42" s="3">
-        <v>100</v>
+      <c r="T42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U42" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V42" s="3">
         <v>200</v>
@@ -3509,8 +3598,8 @@
       <c r="W42" s="3">
         <v>200</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>8</v>
+      <c r="X42" s="3">
+        <v>200</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>8</v>
@@ -3518,8 +3607,8 @@
       <c r="Z42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -3536,8 +3625,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3720,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3667,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3">
         <v>100</v>
@@ -3679,7 +3774,7 @@
         <v>100</v>
       </c>
       <c r="S44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -3720,8 +3815,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3731,8 +3829,8 @@
       <c r="E45" s="3">
         <v>0</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
+      <c r="F45" s="3">
+        <v>0</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
@@ -3746,20 +3844,20 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N45" s="3">
-        <v>100</v>
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -3771,10 +3869,10 @@
         <v>0</v>
       </c>
       <c r="S45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
@@ -3786,34 +3884,37 @@
         <v>0</v>
       </c>
       <c r="X45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
         <v>100</v>
       </c>
       <c r="Z45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA45" s="3">
         <v>900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1200</v>
       </c>
-      <c r="AC45" s="3">
-        <v>100</v>
-      </c>
       <c r="AD45" s="3">
         <v>100</v>
       </c>
       <c r="AE45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF45" s="3">
         <v>200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3821,46 +3922,46 @@
         <v>200</v>
       </c>
       <c r="E46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F46" s="3">
         <v>100</v>
       </c>
       <c r="G46" s="3">
+        <v>100</v>
+      </c>
+      <c r="H46" s="3">
         <v>500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>400</v>
-      </c>
-      <c r="L46" s="3">
-        <v>500</v>
       </c>
       <c r="M46" s="3">
         <v>500</v>
       </c>
       <c r="N46" s="3">
+        <v>500</v>
+      </c>
+      <c r="O46" s="3">
         <v>700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>400</v>
-      </c>
-      <c r="P46" s="3">
-        <v>500</v>
       </c>
       <c r="Q46" s="3">
         <v>500</v>
       </c>
       <c r="R46" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="S46" s="3">
         <v>400</v>
@@ -3869,43 +3970,46 @@
         <v>400</v>
       </c>
       <c r="U46" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="V46" s="3">
         <v>300</v>
       </c>
       <c r="W46" s="3">
+        <v>300</v>
+      </c>
+      <c r="X46" s="3">
         <v>400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3933,21 +4037,21 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>800</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
         <v>200</v>
       </c>
-      <c r="P47" s="3">
-        <v>100</v>
-      </c>
       <c r="Q47" s="3">
         <v>100</v>
       </c>
@@ -3955,10 +4059,10 @@
         <v>100</v>
       </c>
       <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
+      </c>
+      <c r="T47" s="3">
+        <v>0</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>8</v>
@@ -3969,8 +4073,8 @@
       <c r="W47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X47" s="3">
-        <v>200</v>
+      <c r="X47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y47" s="3">
         <v>200</v>
@@ -3979,7 +4083,7 @@
         <v>200</v>
       </c>
       <c r="AA47" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -3996,8 +4100,11 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4017,10 +4124,10 @@
         <v>0</v>
       </c>
       <c r="I48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -4032,23 +4139,23 @@
         <v>0</v>
       </c>
       <c r="N48" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3">
         <v>200</v>
       </c>
       <c r="P48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q48" s="3">
         <v>300</v>
       </c>
       <c r="R48" s="3">
+        <v>300</v>
+      </c>
+      <c r="S48" s="3">
         <v>200</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
       <c r="T48" s="3">
         <v>0</v>
       </c>
@@ -4088,19 +4195,22 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="E49" s="3">
         <v>1900</v>
       </c>
       <c r="F49" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="G49" s="3">
         <v>2000</v>
@@ -4109,13 +4219,13 @@
         <v>2000</v>
       </c>
       <c r="I49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="J49" s="3">
         <v>2100</v>
       </c>
       <c r="K49" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="L49" s="3">
         <v>2200</v>
@@ -4124,64 +4234,67 @@
         <v>2200</v>
       </c>
       <c r="N49" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="O49" s="3">
         <v>2300</v>
       </c>
       <c r="P49" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="Q49" s="3">
         <v>2400</v>
       </c>
       <c r="R49" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="S49" s="3">
         <v>2500</v>
       </c>
       <c r="T49" s="3">
+        <v>2500</v>
+      </c>
+      <c r="U49" s="3">
         <v>4000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4480,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4381,8 +4500,8 @@
       <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>8</v>
+      <c r="H52" s="3">
+        <v>100</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>8</v>
@@ -4390,8 +4509,8 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4403,7 +4522,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
@@ -4414,8 +4533,8 @@
       <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
+      <c r="S52" s="3">
+        <v>100</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>8</v>
@@ -4429,8 +4548,8 @@
       <c r="W52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -4456,8 +4575,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="E54" s="3">
         <v>2100</v>
       </c>
       <c r="F54" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G54" s="3">
         <v>2200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>10000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,13 +4837,14 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
         <v>100</v>
@@ -4723,10 +4853,10 @@
         <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H57" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
@@ -4741,7 +4871,7 @@
         <v>100</v>
       </c>
       <c r="M57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N57" s="3">
         <v>200</v>
@@ -4753,19 +4883,19 @@
         <v>200</v>
       </c>
       <c r="Q57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R57" s="3">
         <v>100</v>
       </c>
       <c r="S57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T57" s="3">
         <v>200</v>
       </c>
       <c r="U57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V57" s="3">
         <v>100</v>
@@ -4777,19 +4907,19 @@
         <v>100</v>
       </c>
       <c r="Y57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z57" s="3">
         <v>200</v>
       </c>
-      <c r="Z57" s="3">
-        <v>100</v>
-      </c>
       <c r="AA57" s="3">
         <v>100</v>
       </c>
       <c r="AB57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC57" s="3">
         <v>300</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>200</v>
       </c>
       <c r="AD57" s="3">
         <v>200</v>
@@ -4798,10 +4928,13 @@
         <v>200</v>
       </c>
       <c r="AF57" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4809,22 +4942,22 @@
         <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F58" s="3">
         <v>400</v>
       </c>
       <c r="G58" s="3">
+        <v>400</v>
+      </c>
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
-        <v>100</v>
-      </c>
       <c r="J58" s="3">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>1200</v>
@@ -4845,13 +4978,13 @@
         <v>1200</v>
       </c>
       <c r="Q58" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="R58" s="3">
         <v>1100</v>
       </c>
       <c r="S58" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="T58" s="3">
         <v>1000</v>
@@ -4860,7 +4993,7 @@
         <v>1000</v>
       </c>
       <c r="V58" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="W58" s="3">
         <v>900</v>
@@ -4869,31 +5002,34 @@
         <v>900</v>
       </c>
       <c r="Y58" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="Z58" s="3">
         <v>800</v>
       </c>
       <c r="AA58" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB58" s="3">
         <v>600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>300</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>500</v>
       </c>
       <c r="AE58" s="3">
         <v>500</v>
       </c>
       <c r="AF58" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG58" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4916,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K59" s="3">
         <v>200</v>
@@ -4928,72 +5064,75 @@
         <v>200</v>
       </c>
       <c r="N59" s="3">
+        <v>200</v>
+      </c>
+      <c r="O59" s="3">
         <v>300</v>
-      </c>
-      <c r="O59" s="3">
-        <v>200</v>
       </c>
       <c r="P59" s="3">
         <v>200</v>
       </c>
       <c r="Q59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T59" s="3">
+      <c r="S59" s="3">
+        <v>100</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U59" s="3">
         <v>500</v>
-      </c>
-      <c r="U59" s="3">
-        <v>400</v>
       </c>
       <c r="V59" s="3">
         <v>400</v>
       </c>
       <c r="W59" s="3">
+        <v>400</v>
+      </c>
+      <c r="X59" s="3">
         <v>500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1000</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>800</v>
       </c>
       <c r="AA59" s="3">
         <v>800</v>
       </c>
       <c r="AB59" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC59" s="3">
         <v>1000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>500</v>
       </c>
-      <c r="AD59" s="3">
-        <v>100</v>
-      </c>
       <c r="AE59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF59" s="3">
         <v>200</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>500</v>
+      </c>
+      <c r="E60" s="3">
         <v>400</v>
-      </c>
-      <c r="E60" s="3">
-        <v>500</v>
       </c>
       <c r="F60" s="3">
         <v>500</v>
@@ -5002,16 +5141,16 @@
         <v>500</v>
       </c>
       <c r="H60" s="3">
+        <v>600</v>
+      </c>
+      <c r="I60" s="3">
         <v>400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1600</v>
-      </c>
-      <c r="K60" s="3">
-        <v>1500</v>
       </c>
       <c r="L60" s="3">
         <v>1500</v>
@@ -5020,64 +5159,67 @@
         <v>1500</v>
       </c>
       <c r="N60" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="O60" s="3">
         <v>1600</v>
       </c>
       <c r="P60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q60" s="3">
         <v>1500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1600</v>
-      </c>
-      <c r="U60" s="3">
-        <v>1500</v>
       </c>
       <c r="V60" s="3">
         <v>1500</v>
       </c>
       <c r="W60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X60" s="3">
         <v>1600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5168,35 +5310,38 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>800</v>
+      </c>
+      <c r="E62" s="3">
         <v>700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>400</v>
       </c>
       <c r="G62" s="3">
         <v>400</v>
       </c>
       <c r="H62" s="3">
+        <v>400</v>
+      </c>
+      <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>200</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5219,11 +5364,11 @@
         <v>0</v>
       </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
         <v>600</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5239,8 +5384,8 @@
       <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -5260,8 +5405,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,34 +5690,37 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2300</v>
       </c>
-      <c r="G66" s="3">
-        <v>2200</v>
-      </c>
       <c r="H66" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I66" s="3">
         <v>1900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3100</v>
-      </c>
-      <c r="K66" s="3">
-        <v>2900</v>
       </c>
       <c r="L66" s="3">
         <v>2900</v>
@@ -5572,7 +5729,7 @@
         <v>2900</v>
       </c>
       <c r="N66" s="3">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="O66" s="3">
         <v>2600</v>
@@ -5581,55 +5738,58 @@
         <v>2600</v>
       </c>
       <c r="Q66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="R66" s="3">
         <v>2700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2800</v>
-      </c>
-      <c r="U66" s="3">
-        <v>2700</v>
       </c>
       <c r="V66" s="3">
         <v>2700</v>
       </c>
       <c r="W66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="X66" s="3">
         <v>2800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-82100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-81700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-81500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-81100</v>
       </c>
-      <c r="G72" s="3">
-        <v>-80600</v>
-      </c>
       <c r="H72" s="3">
+        <v>-80700</v>
+      </c>
+      <c r="I72" s="3">
         <v>-80000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-79900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-79600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-79500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-79100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-77900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-77400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-77000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-76500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-76000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-75500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-74900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-72700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-72200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-71600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-70900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-69600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-68800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-67800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-66800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-64200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-63200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-61200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-59200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-54900</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,40 +6580,43 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-100</v>
       </c>
-      <c r="G76" s="3">
-        <v>400</v>
-      </c>
       <c r="H76" s="3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="I76" s="3">
         <v>1000</v>
       </c>
       <c r="J76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K76" s="3">
         <v>-400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-200</v>
-      </c>
-      <c r="M76" s="3">
-        <v>700</v>
       </c>
       <c r="N76" s="3">
         <v>700</v>
@@ -6449,49 +6634,52 @@
         <v>700</v>
       </c>
       <c r="S76" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="T76" s="3">
+        <v>0</v>
+      </c>
+      <c r="U76" s="3">
         <v>1600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-600</v>
       </c>
-      <c r="H81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="R81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="S81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="U81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="X81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-400</v>
       </c>
-      <c r="J81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-400</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="Z81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AA81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AB81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="AC81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AD81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AE81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AF81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-500</v>
       </c>
-      <c r="P81" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-600</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-500</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-700</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6838,7 +7036,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
@@ -6874,17 +7072,17 @@
         <v>100</v>
       </c>
       <c r="Y83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z83" s="3">
         <v>300</v>
       </c>
-      <c r="Z83" s="3">
-        <v>100</v>
-      </c>
       <c r="AA83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB83" s="3">
         <v>200</v>
       </c>
-      <c r="AB83" s="3">
-        <v>100</v>
-      </c>
       <c r="AC83" s="3">
         <v>100</v>
       </c>
@@ -6892,13 +7090,16 @@
         <v>100</v>
       </c>
       <c r="AE83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF83" s="3">
         <v>300</v>
       </c>
-      <c r="AF83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,8 +7570,11 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7366,25 +7582,25 @@
         <v>0</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
         <v>-100</v>
       </c>
       <c r="I89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J89" s="3">
         <v>0</v>
       </c>
       <c r="K89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L89" s="3">
         <v>-100</v>
@@ -7396,28 +7612,28 @@
         <v>-100</v>
       </c>
       <c r="O89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
-        <v>100</v>
-      </c>
       <c r="T89" s="3">
         <v>100</v>
       </c>
       <c r="U89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W89" s="3">
         <v>-100</v>
@@ -7426,22 +7642,22 @@
         <v>-100</v>
       </c>
       <c r="Y89" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="Z89" s="3">
         <v>-400</v>
       </c>
       <c r="AA89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>-100</v>
       </c>
       <c r="AE89" s="3">
         <v>-100</v>
@@ -7449,8 +7665,11 @@
       <c r="AF89" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7518,32 +7738,32 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>8</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -7560,8 +7780,8 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>8</v>
+      <c r="AB91" s="3">
+        <v>0</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>8</v>
@@ -7569,14 +7789,17 @@
       <c r="AD91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +7985,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7774,11 +8003,11 @@
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
@@ -7810,11 +8039,11 @@
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
@@ -7840,19 +8069,22 @@
         <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-200</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8495,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8268,13 +8513,13 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
         <v>100</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -8286,16 +8531,16 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N100" s="3">
         <v>100</v>
       </c>
       <c r="O100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="3">
         <v>100</v>
@@ -8307,7 +8552,7 @@
         <v>100</v>
       </c>
       <c r="T100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -8316,37 +8561,40 @@
         <v>0</v>
       </c>
       <c r="W100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>400</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>300</v>
       </c>
       <c r="AA100" s="3">
         <v>300</v>
       </c>
       <c r="AB100" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AC100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>300</v>
       </c>
-      <c r="AF100" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,26 +8685,29 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
@@ -8464,11 +8715,11 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
@@ -8476,57 +8727,60 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>400</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T102" s="3">
+        <v>100</v>
+      </c>
+      <c r="U102" s="3">
         <v>200</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W102" s="3">
         <v>-100</v>
       </c>
       <c r="X102" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="Y102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Z102" s="3">
         <v>-100</v>
       </c>
       <c r="AA102" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="AB102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CBDS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBDS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>CBDS</t>
   </si>
@@ -656,143 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -800,10 +808,10 @@
         <v>200</v>
       </c>
       <c r="E8" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F8" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G8" s="3">
         <v>300</v>
@@ -812,73 +820,73 @@
         <v>300</v>
       </c>
       <c r="I8" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J8" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="K8" s="3">
         <v>400</v>
       </c>
       <c r="L8" s="3">
+        <v>500</v>
+      </c>
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
-        <v>500</v>
-      </c>
       <c r="N8" s="3">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="O8" s="3">
         <v>500</v>
       </c>
       <c r="P8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>500</v>
+      </c>
+      <c r="R8" s="3">
         <v>300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1200</v>
-      </c>
-      <c r="S8" s="3">
-        <v>500</v>
-      </c>
-      <c r="T8" s="3">
-        <v>500</v>
       </c>
       <c r="U8" s="3">
         <v>500</v>
       </c>
       <c r="V8" s="3">
+        <v>500</v>
+      </c>
+      <c r="W8" s="3">
+        <v>500</v>
+      </c>
+      <c r="X8" s="3">
         <v>200</v>
       </c>
-      <c r="W8" s="3">
-        <v>100</v>
-      </c>
-      <c r="X8" s="3">
-        <v>100</v>
-      </c>
       <c r="Y8" s="3">
         <v>100</v>
       </c>
       <c r="Z8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB8" s="3">
         <v>300</v>
       </c>
-      <c r="AA8" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD8" s="3">
         <v>200</v>
       </c>
-      <c r="AC8" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>0</v>
-      </c>
       <c r="AE8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF8" s="3">
         <v>0</v>
@@ -886,8 +894,14 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -910,70 +924,70 @@
         <v>100</v>
       </c>
       <c r="J9" s="3">
+        <v>100</v>
+      </c>
+      <c r="K9" s="3">
+        <v>100</v>
+      </c>
+      <c r="L9" s="3">
         <v>200</v>
-      </c>
-      <c r="K9" s="3">
-        <v>200</v>
-      </c>
-      <c r="L9" s="3">
-        <v>100</v>
       </c>
       <c r="M9" s="3">
         <v>200</v>
       </c>
       <c r="N9" s="3">
+        <v>100</v>
+      </c>
+      <c r="O9" s="3">
+        <v>200</v>
+      </c>
+      <c r="P9" s="3">
         <v>400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>200</v>
-      </c>
       <c r="R9" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="S9" s="3">
         <v>200</v>
       </c>
       <c r="T9" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="U9" s="3">
         <v>200</v>
       </c>
       <c r="V9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W9" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB9" s="3">
         <v>100</v>
       </c>
       <c r="AC9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF9" s="3">
         <v>0</v>
@@ -981,8 +995,14 @@
       <c r="AG9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -990,10 +1010,10 @@
         <v>100</v>
       </c>
       <c r="E10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3">
         <v>200</v>
@@ -1002,70 +1022,70 @@
         <v>200</v>
       </c>
       <c r="I10" s="3">
+        <v>200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>200</v>
+      </c>
+      <c r="K10" s="3">
         <v>300</v>
-      </c>
-      <c r="J10" s="3">
-        <v>300</v>
-      </c>
-      <c r="K10" s="3">
-        <v>200</v>
       </c>
       <c r="L10" s="3">
         <v>300</v>
       </c>
       <c r="M10" s="3">
+        <v>200</v>
+      </c>
+      <c r="N10" s="3">
         <v>300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
+        <v>300</v>
+      </c>
+      <c r="P10" s="3">
         <v>600</v>
       </c>
-      <c r="O10" s="3">
-        <v>100</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
+        <v>100</v>
+      </c>
+      <c r="R10" s="3">
         <v>200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>800</v>
-      </c>
-      <c r="S10" s="3">
-        <v>300</v>
-      </c>
-      <c r="T10" s="3">
-        <v>300</v>
       </c>
       <c r="U10" s="3">
         <v>300</v>
       </c>
       <c r="V10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="W10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X10" s="3">
         <v>100</v>
       </c>
       <c r="Y10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="3">
         <v>200</v>
       </c>
-      <c r="AA10" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>100</v>
-      </c>
       <c r="AC10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE10" s="3">
         <v>0</v>
@@ -1076,8 +1096,14 @@
       <c r="AG10" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1137,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1234,14 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,103 +1335,115 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>1400</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1200</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>900</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1432,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1441,7 +1487,7 @@
         <v>100</v>
       </c>
       <c r="Q15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R15" s="3">
         <v>100</v>
@@ -1449,11 +1495,11 @@
       <c r="S15" s="3">
         <v>100</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>8</v>
+      <c r="T15" s="3">
+        <v>100</v>
+      </c>
+      <c r="U15" s="3">
+        <v>100</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>8</v>
@@ -1464,11 +1510,11 @@
       <c r="X15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1491,8 +1537,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1575,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E17" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F17" s="3">
         <v>600</v>
       </c>
       <c r="G17" s="3">
+        <v>600</v>
+      </c>
+      <c r="H17" s="3">
+        <v>600</v>
+      </c>
+      <c r="I17" s="3">
         <v>500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>800</v>
-      </c>
-      <c r="I17" s="3">
-        <v>800</v>
-      </c>
-      <c r="J17" s="3">
-        <v>600</v>
       </c>
       <c r="K17" s="3">
         <v>800</v>
       </c>
       <c r="L17" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="M17" s="3">
         <v>800</v>
       </c>
       <c r="N17" s="3">
+        <v>800</v>
+      </c>
+      <c r="O17" s="3">
+        <v>800</v>
+      </c>
+      <c r="P17" s="3">
         <v>2000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>2000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-100</v>
       </c>
       <c r="K18" s="3">
         <v>-400</v>
       </c>
       <c r="L18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M18" s="3">
         <v>-400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-1000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-2000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,28 +1814,30 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>300</v>
       </c>
       <c r="J20" s="3">
         <v>-200</v>
@@ -1778,41 +1846,41 @@
         <v>300</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="M20" s="3">
+        <v>300</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-800</v>
-      </c>
-      <c r="N20" s="3">
-        <v>200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>200</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1820,17 +1888,17 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -1843,114 +1911,126 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="E21" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="F21" s="3">
         <v>-300</v>
       </c>
       <c r="G21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-700</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-600</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-300</v>
       </c>
       <c r="Q21" s="3">
         <v>-300</v>
       </c>
       <c r="R21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T21" s="3">
         <v>-700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-2000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-400</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-1800</v>
       </c>
       <c r="Y21" s="3">
         <v>-600</v>
       </c>
       <c r="Z21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-1900</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>-2500</v>
       </c>
       <c r="AC21" s="3">
         <v>-1000</v>
       </c>
       <c r="AD21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>200</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -2012,14 +2092,14 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -2028,18 +2108,24 @@
         <v>0</v>
       </c>
       <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
         <v>300</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E23" s="3">
         <v>-200</v>
@@ -2048,88 +2134,94 @@
         <v>-300</v>
       </c>
       <c r="G23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I23" s="3">
         <v>-500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-300</v>
       </c>
       <c r="K23" s="3">
         <v>-100</v>
       </c>
       <c r="L23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-2200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2200</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-2700</v>
       </c>
       <c r="AC23" s="3">
         <v>-1100</v>
       </c>
       <c r="AD23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2223,8 +2315,14 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,13 +2416,19 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E26" s="3">
         <v>-200</v>
@@ -2333,93 +2437,99 @@
         <v>-300</v>
       </c>
       <c r="G26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I26" s="3">
         <v>-500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-800</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-300</v>
       </c>
       <c r="K26" s="3">
         <v>-100</v>
       </c>
       <c r="L26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-2200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2200</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-2700</v>
       </c>
       <c r="AC26" s="3">
         <v>-1100</v>
       </c>
       <c r="AD26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E27" s="3">
         <v>-200</v>
@@ -2428,16 +2538,16 @@
         <v>-300</v>
       </c>
       <c r="G27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I27" s="3">
         <v>-500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-700</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-400</v>
       </c>
       <c r="K27" s="3">
         <v>-100</v>
@@ -2446,70 +2556,76 @@
         <v>-400</v>
       </c>
       <c r="M27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O27" s="3">
         <v>-1200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-800</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-300</v>
       </c>
       <c r="Q27" s="3">
         <v>-300</v>
       </c>
       <c r="R27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T27" s="3">
         <v>-800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2620,11 +2742,11 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2639,29 +2761,29 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>-200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>-200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>-300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>-100</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
@@ -2680,11 +2802,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2692,14 +2814,20 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,28 +3022,34 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-300</v>
       </c>
       <c r="J32" s="3">
         <v>200</v>
@@ -2918,40 +3058,40 @@
         <v>-300</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>800</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-200</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
@@ -2960,17 +3100,17 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
@@ -2983,13 +3123,19 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E33" s="3">
         <v>-200</v>
@@ -2998,16 +3144,16 @@
         <v>-300</v>
       </c>
       <c r="G33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I33" s="3">
         <v>-500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-700</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-400</v>
       </c>
       <c r="K33" s="3">
         <v>-100</v>
@@ -3016,70 +3162,76 @@
         <v>-400</v>
       </c>
       <c r="M33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O33" s="3">
         <v>-1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-500</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-600</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-1100</v>
       </c>
       <c r="S33" s="3">
         <v>-600</v>
       </c>
       <c r="T33" s="3">
-        <v>-2100</v>
+        <v>-1100</v>
       </c>
       <c r="U33" s="3">
         <v>-600</v>
       </c>
       <c r="V33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="W33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,13 +3325,19 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E35" s="3">
         <v>-200</v>
@@ -3188,16 +3346,16 @@
         <v>-300</v>
       </c>
       <c r="G35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I35" s="3">
         <v>-500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-700</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-400</v>
       </c>
       <c r="K35" s="3">
         <v>-100</v>
@@ -3206,170 +3364,182 @@
         <v>-400</v>
       </c>
       <c r="M35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O35" s="3">
         <v>-1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-500</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-600</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-1100</v>
       </c>
       <c r="S35" s="3">
         <v>-600</v>
       </c>
       <c r="T35" s="3">
-        <v>-2100</v>
+        <v>-1100</v>
       </c>
       <c r="U35" s="3">
         <v>-600</v>
       </c>
       <c r="V35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="W35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,8 +3610,10 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3459,10 +3633,10 @@
         <v>100</v>
       </c>
       <c r="I41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K41" s="3">
         <v>200</v>
@@ -3471,10 +3645,10 @@
         <v>200</v>
       </c>
       <c r="M41" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N41" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O41" s="3">
         <v>300</v>
@@ -3483,105 +3657,111 @@
         <v>300</v>
       </c>
       <c r="Q41" s="3">
+        <v>300</v>
+      </c>
+      <c r="R41" s="3">
+        <v>300</v>
+      </c>
+      <c r="S41" s="3">
         <v>400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>200</v>
       </c>
-      <c r="V41" s="3">
-        <v>100</v>
-      </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
       <c r="X41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>200</v>
       </c>
-      <c r="Z41" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>100</v>
-      </c>
       <c r="AB41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD41" s="3">
         <v>200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>300</v>
       </c>
-      <c r="AG41" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>500</v>
-      </c>
-      <c r="L42" s="3">
-        <v>200</v>
-      </c>
-      <c r="M42" s="3">
-        <v>200</v>
       </c>
       <c r="N42" s="3">
         <v>200</v>
       </c>
       <c r="O42" s="3">
+        <v>200</v>
+      </c>
+      <c r="P42" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q42" s="3">
         <v>300</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>8</v>
+      <c r="R42" s="3">
+        <v>0</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>8</v>
@@ -3589,32 +3769,32 @@
       <c r="T42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U42" s="3">
-        <v>100</v>
-      </c>
-      <c r="V42" s="3">
-        <v>200</v>
+      <c r="U42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W42" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X42" s="3">
         <v>200</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>8</v>
+      <c r="Y42" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>200</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -3628,8 +3808,14 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3723,8 +3909,14 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3765,10 +3957,10 @@
         <v>0</v>
       </c>
       <c r="P44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R44" s="3">
         <v>100</v>
@@ -3777,10 +3969,10 @@
         <v>100</v>
       </c>
       <c r="T44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -3818,8 +4010,14 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3832,11 +4030,11 @@
       <c r="F45" s="3">
         <v>0</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
@@ -3847,23 +4045,23 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
+        <v>0</v>
       </c>
       <c r="O45" s="3">
-        <v>100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -3872,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="T45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
       </c>
       <c r="V45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -3887,129 +4085,141 @@
         <v>0</v>
       </c>
       <c r="Y45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC45" s="3">
         <v>900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1200</v>
       </c>
-      <c r="AD45" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>100</v>
-      </c>
       <c r="AF45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH45" s="3">
         <v>200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>100</v>
+      </c>
+      <c r="F46" s="3">
         <v>200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>200</v>
       </c>
-      <c r="F46" s="3">
-        <v>100</v>
-      </c>
-      <c r="G46" s="3">
-        <v>100</v>
-      </c>
       <c r="H46" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="I46" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="J46" s="3">
         <v>500</v>
       </c>
       <c r="K46" s="3">
+        <v>800</v>
+      </c>
+      <c r="L46" s="3">
+        <v>500</v>
+      </c>
+      <c r="M46" s="3">
         <v>600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>500</v>
-      </c>
-      <c r="S46" s="3">
-        <v>400</v>
-      </c>
-      <c r="T46" s="3">
-        <v>400</v>
       </c>
       <c r="U46" s="3">
         <v>400</v>
       </c>
       <c r="V46" s="3">
+        <v>400</v>
+      </c>
+      <c r="W46" s="3">
+        <v>400</v>
+      </c>
+      <c r="X46" s="3">
         <v>300</v>
-      </c>
-      <c r="W46" s="3">
-        <v>300</v>
-      </c>
-      <c r="X46" s="3">
-        <v>400</v>
       </c>
       <c r="Y46" s="3">
         <v>300</v>
       </c>
       <c r="Z46" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA46" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB46" s="3">
         <v>200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1400</v>
-      </c>
-      <c r="AD46" s="3">
-        <v>500</v>
-      </c>
-      <c r="AE46" s="3">
-        <v>1000</v>
       </c>
       <c r="AF46" s="3">
         <v>500</v>
       </c>
       <c r="AG46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI46" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4040,35 +4250,35 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
+      <c r="M47" s="3">
+        <v>0</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
         <v>800</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
         <v>200</v>
       </c>
-      <c r="Q47" s="3">
-        <v>100</v>
-      </c>
-      <c r="R47" s="3">
-        <v>100</v>
-      </c>
       <c r="S47" s="3">
         <v>100</v>
       </c>
       <c r="T47" s="3">
-        <v>0</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
+      </c>
+      <c r="U47" s="3">
+        <v>100</v>
+      </c>
+      <c r="V47" s="3">
+        <v>0</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>8</v>
@@ -4076,20 +4286,20 @@
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y47" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>200</v>
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA47" s="3">
         <v>200</v>
       </c>
       <c r="AB47" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AC47" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
@@ -4103,8 +4313,14 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4127,13 +4343,13 @@
         <v>0</v>
       </c>
       <c r="J48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
       </c>
       <c r="L48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -4142,26 +4358,26 @@
         <v>0</v>
       </c>
       <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3">
         <v>200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>200</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
-      </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
       <c r="V48" s="3">
         <v>0</v>
       </c>
@@ -4198,8 +4414,14 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4207,94 +4429,100 @@
         <v>1800</v>
       </c>
       <c r="E49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G49" s="3">
         <v>1900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1900</v>
-      </c>
-      <c r="G49" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>2000</v>
       </c>
       <c r="I49" s="3">
         <v>2000</v>
       </c>
       <c r="J49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L49" s="3">
         <v>2100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2100</v>
-      </c>
-      <c r="L49" s="3">
-        <v>2200</v>
-      </c>
-      <c r="M49" s="3">
-        <v>2200</v>
       </c>
       <c r="N49" s="3">
         <v>2200</v>
       </c>
       <c r="O49" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P49" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q49" s="3">
         <v>2300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>4000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>4200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>4300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>4500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>5800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>5900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>6100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>6200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>8600</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>3200</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>3100</v>
       </c>
       <c r="AF49" s="3">
         <v>3200</v>
       </c>
       <c r="AG49" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AI49" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,8 +4717,14 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4503,20 +4743,20 @@
       <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
+      <c r="I52" s="3">
+        <v>100</v>
+      </c>
+      <c r="J52" s="3">
+        <v>100</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -4525,10 +4765,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R52" s="3">
         <v>100</v>
@@ -4536,11 +4776,11 @@
       <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>8</v>
+      <c r="T52" s="3">
+        <v>100</v>
+      </c>
+      <c r="U52" s="3">
+        <v>100</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>8</v>
@@ -4551,11 +4791,11 @@
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
@@ -4578,8 +4818,14 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,34 +4919,40 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F54" s="3">
         <v>2000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2200</v>
-      </c>
-      <c r="H54" s="3">
-        <v>2600</v>
-      </c>
-      <c r="I54" s="3">
-        <v>2900</v>
       </c>
       <c r="J54" s="3">
         <v>2600</v>
       </c>
       <c r="K54" s="3">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="L54" s="3">
         <v>2600</v>
@@ -4709,67 +4961,73 @@
         <v>2700</v>
       </c>
       <c r="N54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="O54" s="3">
+        <v>2700</v>
+      </c>
+      <c r="P54" s="3">
         <v>3500</v>
-      </c>
-      <c r="O54" s="3">
-        <v>3300</v>
-      </c>
-      <c r="P54" s="3">
-        <v>3200</v>
       </c>
       <c r="Q54" s="3">
         <v>3300</v>
       </c>
       <c r="R54" s="3">
+        <v>3200</v>
+      </c>
+      <c r="S54" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T54" s="3">
         <v>3400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>3200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>4400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>4500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>4600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>4900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>6300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>6400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>7200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>7700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>10000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>3800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>4100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>3700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,32 +5098,34 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
-        <v>100</v>
-      </c>
       <c r="F57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G57" s="3">
         <v>100</v>
       </c>
       <c r="H57" s="3">
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
+        <v>100</v>
+      </c>
+      <c r="J57" s="3">
         <v>300</v>
       </c>
-      <c r="I57" s="3">
-        <v>100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>100</v>
-      </c>
       <c r="K57" s="3">
         <v>100</v>
       </c>
@@ -4874,10 +5136,10 @@
         <v>100</v>
       </c>
       <c r="N57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
@@ -4886,23 +5148,23 @@
         <v>200</v>
       </c>
       <c r="R57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T57" s="3">
+        <v>100</v>
+      </c>
+      <c r="U57" s="3">
+        <v>100</v>
+      </c>
+      <c r="V57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3">
-        <v>100</v>
-      </c>
-      <c r="W57" s="3">
-        <v>100</v>
-      </c>
       <c r="X57" s="3">
         <v>100</v>
       </c>
@@ -4910,60 +5172,66 @@
         <v>100</v>
       </c>
       <c r="Z57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AA57" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>100</v>
-      </c>
       <c r="AC57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE57" s="3">
         <v>300</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>200</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>200</v>
       </c>
       <c r="AF57" s="3">
         <v>200</v>
       </c>
       <c r="AG57" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>400</v>
+      </c>
+      <c r="F58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>200</v>
       </c>
-      <c r="J58" s="3">
-        <v>100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1200</v>
-      </c>
       <c r="L58" s="3">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
         <v>1200</v>
@@ -4981,55 +5249,61 @@
         <v>1200</v>
       </c>
       <c r="R58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="T58" s="3">
         <v>1100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1100</v>
-      </c>
-      <c r="T58" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U58" s="3">
-        <v>1000</v>
       </c>
       <c r="V58" s="3">
         <v>1000</v>
       </c>
       <c r="W58" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="X58" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="Y58" s="3">
         <v>900</v>
       </c>
       <c r="Z58" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>900</v>
+      </c>
+      <c r="AB58" s="3">
         <v>800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5055,10 +5329,10 @@
         <v>0</v>
       </c>
       <c r="K59" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L59" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M59" s="3">
         <v>200</v>
@@ -5067,159 +5341,171 @@
         <v>200</v>
       </c>
       <c r="O59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P59" s="3">
         <v>200</v>
       </c>
       <c r="Q59" s="3">
+        <v>300</v>
+      </c>
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3">
-        <v>100</v>
-      </c>
       <c r="S59" s="3">
-        <v>100</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>8</v>
+        <v>200</v>
+      </c>
+      <c r="T59" s="3">
+        <v>100</v>
       </c>
       <c r="U59" s="3">
+        <v>100</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W59" s="3">
         <v>500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>500</v>
       </c>
-      <c r="AE59" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH59" s="3">
         <v>200</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E60" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F60" s="3">
         <v>500</v>
       </c>
       <c r="G60" s="3">
+        <v>400</v>
+      </c>
+      <c r="H60" s="3">
         <v>500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>500</v>
+      </c>
+      <c r="J60" s="3">
         <v>600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1600</v>
-      </c>
-      <c r="L60" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M60" s="3">
-        <v>1500</v>
       </c>
       <c r="N60" s="3">
         <v>1500</v>
       </c>
       <c r="O60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q60" s="3">
         <v>1600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>2300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>1000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5313,31 +5599,37 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>900</v>
+      </c>
+      <c r="E62" s="3">
         <v>800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
+        <v>800</v>
+      </c>
+      <c r="G62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>200</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
       </c>
       <c r="K62" s="3">
         <v>200</v>
@@ -5346,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -5367,14 +5659,14 @@
         <v>0</v>
       </c>
       <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>600</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5387,11 +5679,11 @@
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -5408,8 +5700,14 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +6003,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F66" s="3">
         <v>2600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3100</v>
-      </c>
-      <c r="L66" s="3">
-        <v>2900</v>
-      </c>
-      <c r="M66" s="3">
-        <v>2900</v>
       </c>
       <c r="N66" s="3">
         <v>2900</v>
       </c>
       <c r="O66" s="3">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="P66" s="3">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="Q66" s="3">
         <v>2600</v>
       </c>
       <c r="R66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="S66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="T66" s="3">
         <v>2700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>2500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>2700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>4100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>3900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>3600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>3500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>4900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6545,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-82700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-82300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-82100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-81700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-81500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-81100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-80700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-80000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-79900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-79600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-79500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-79100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-77900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-77400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-77000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-76500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-76000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-75500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-74900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-72700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-72200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-71600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-70900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-69600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-68800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-67800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-66800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-64200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-63200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-61200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-59200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-54900</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,46 +6949,52 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F76" s="3">
         <v>-600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-200</v>
-      </c>
-      <c r="N76" s="3">
-        <v>700</v>
-      </c>
-      <c r="O76" s="3">
-        <v>700</v>
       </c>
       <c r="P76" s="3">
         <v>700</v>
@@ -6637,49 +7009,55 @@
         <v>700</v>
       </c>
       <c r="T76" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="U76" s="3">
+        <v>700</v>
+      </c>
+      <c r="V76" s="3">
+        <v>0</v>
+      </c>
+      <c r="W76" s="3">
         <v>1600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>2100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>2200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>2500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>3600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>4200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>5100</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>2600</v>
-      </c>
-      <c r="AE76" s="3">
-        <v>3200</v>
       </c>
       <c r="AF76" s="3">
         <v>2600</v>
       </c>
       <c r="AG76" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AH76" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AI76" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,113 +7151,125 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E81" s="3">
         <v>-200</v>
@@ -6888,16 +7278,16 @@
         <v>-300</v>
       </c>
       <c r="G81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I81" s="3">
         <v>-500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-700</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-400</v>
       </c>
       <c r="K81" s="3">
         <v>-100</v>
@@ -6906,70 +7296,76 @@
         <v>-400</v>
       </c>
       <c r="M81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O81" s="3">
         <v>-1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-500</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-600</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-1100</v>
       </c>
       <c r="S81" s="3">
         <v>-600</v>
       </c>
       <c r="T81" s="3">
-        <v>-2100</v>
+        <v>-1100</v>
       </c>
       <c r="U81" s="3">
         <v>-600</v>
       </c>
       <c r="V81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="W81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7399,10 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7039,10 +7437,10 @@
         <v>0</v>
       </c>
       <c r="N83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
@@ -7075,31 +7473,37 @@
         <v>100</v>
       </c>
       <c r="Z83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB83" s="3">
         <v>300</v>
       </c>
-      <c r="AA83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD83" s="3">
         <v>200</v>
       </c>
-      <c r="AC83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>100</v>
-      </c>
       <c r="AE83" s="3">
         <v>100</v>
       </c>
       <c r="AF83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH83" s="3">
         <v>300</v>
       </c>
-      <c r="AG83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,8 +8001,14 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7585,7 +8019,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G89" s="3">
         <v>0</v>
@@ -7594,19 +8028,19 @@
         <v>-100</v>
       </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N89" s="3">
         <v>-100</v>
@@ -7615,61 +8049,67 @@
         <v>-100</v>
       </c>
       <c r="P89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R89" s="3">
         <v>-700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3">
-        <v>100</v>
-      </c>
-      <c r="U89" s="3">
-        <v>100</v>
-      </c>
       <c r="V89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W89" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="X89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y89" s="3">
         <v>-100</v>
       </c>
       <c r="Z89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>-100</v>
       </c>
       <c r="AG89" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI89" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +8143,10 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7741,35 +8183,35 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>8</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -7783,23 +8225,29 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD91" s="3" t="s">
-        <v>8</v>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,8 +8442,14 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8006,14 +8466,14 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
@@ -8042,14 +8502,14 @@
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
@@ -8072,19 +8532,25 @@
         <v>0</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-200</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8584,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8681,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,8 +8984,14 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8516,16 +9008,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -8534,19 +9026,19 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q100" s="3">
         <v>100</v>
       </c>
       <c r="R100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S100" s="3">
         <v>100</v>
@@ -8555,46 +9047,52 @@
         <v>100</v>
       </c>
       <c r="U100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
       <c r="X100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA100" s="3">
         <v>200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>300</v>
       </c>
-      <c r="AC100" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>300</v>
       </c>
-      <c r="AG100" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,8 +9186,14 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8697,90 +9201,96 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>400</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3">
-        <v>100</v>
-      </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
+        <v>100</v>
+      </c>
+      <c r="W102" s="3">
         <v>200</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-100</v>
-      </c>
-      <c r="X102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>100</v>
       </c>
       <c r="Z102" s="3">
         <v>-100</v>
       </c>
       <c r="AA102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
-        <v>100</v>
-      </c>
       <c r="AC102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
